--- a/PPG/Editais.xlsx
+++ b/PPG/Editais.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C515732B-2D3D-7646-8E01-4F3FA301B174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0741C70D-608D-714C-B7E7-0F8F43BD26DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="680" windowWidth="27640" windowHeight="16900" xr2:uid="{46CBE343-25B5-CE4C-8D60-80361989358C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="210">
   <si>
     <t>Publicação</t>
   </si>
@@ -663,6 +663,12 @@
   </si>
   <si>
     <t>2026-1 PPGCR Edital N° 5.pdf</t>
+  </si>
+  <si>
+    <t>2026 UNISUAM IC Aunos.pdf</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1oK8x_s7LZ_d7S2zUUV52sOmBnfiMHH5T</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1051,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{109E75EB-4039-C840-A144-16CD29903E29}">
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.83203125" style="3" bestFit="1" customWidth="1"/>
@@ -1847,12 +1853,23 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B73" t="s">
+        <v>208</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B74" t="s">
         <v>207</v>
       </c>
-      <c r="C73" s="5" t="s">
+      <c r="C74" s="5" t="s">
         <v>205</v>
       </c>
     </row>
@@ -1933,7 +1950,8 @@
     <hyperlink ref="C70" r:id="rId69" xr:uid="{DC3BB191-A02F-DA46-BF70-86BF90F77374}"/>
     <hyperlink ref="C71" r:id="rId70" xr:uid="{1613F4D7-EBC8-0F44-8E5C-4ECB9A8FE0E7}"/>
     <hyperlink ref="C72" r:id="rId71" xr:uid="{5D1CAD7F-C422-5140-959C-31633A8FD51F}"/>
-    <hyperlink ref="C73" r:id="rId72" xr:uid="{851FFC45-6AFE-8C4E-B2A3-5E0512776E28}"/>
+    <hyperlink ref="C74" r:id="rId72" xr:uid="{851FFC45-6AFE-8C4E-B2A3-5E0512776E28}"/>
+    <hyperlink ref="C73" r:id="rId73" xr:uid="{0F4ABF96-7FB6-F049-BA32-4FC1FA09F375}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
